--- a/表格模版/依诺达.xlsx
+++ b/表格模版/依诺达.xlsx
@@ -4,16 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32660" windowHeight="8460"/>
+    <workbookView windowWidth="24460" windowHeight="9600"/>
   </bookViews>
   <sheets>
-    <sheet name="模板" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">模板!$A$16:$Q$17</definedName>
-  </definedNames>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -63,7 +60,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-采购单价换成美金申报</t>
+按采购单价换算
+</t>
         </r>
       </text>
     </comment>
@@ -72,15 +70,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="105">
   <si>
     <t>客户订单号*</t>
   </si>
   <si>
-    <t>AX-90045</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>带电</t>
     </r>
     <r>
@@ -99,6 +101,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>使用说明：</t>
     </r>
     <r>
@@ -143,10 +151,14 @@
     <t>服务*</t>
   </si>
   <si>
-    <t>罗马尼亚铁路</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>带磁</t>
     </r>
     <r>
@@ -165,6 +177,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>液体</t>
     </r>
     <r>
@@ -186,6 +205,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>粉末</t>
     </r>
     <r>
@@ -204,6 +230,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>危险品</t>
     </r>
     <r>
@@ -221,10 +254,17 @@
     <t>收件人地址一*</t>
   </si>
   <si>
-    <t>Strada Ciorogarla 214, sat Bacu, Comuna Joita, judet Giurgiu, Rampa N37-38</t>
+    <t>StradaCiorogarla214,RampaS35-S36</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>报关方式</t>
     </r>
     <r>
@@ -251,7 +291,7 @@
     <t>收件人城市*</t>
   </si>
   <si>
-    <t>comuna Joita, sat Bacu</t>
+    <t>Bâcu</t>
   </si>
   <si>
     <t>交税方式*</t>
@@ -281,21 +321,30 @@
     <t>收件人国家代码(二字代码)*</t>
   </si>
   <si>
-    <t>RO</t>
+    <t>Ro</t>
+  </si>
+  <si>
+    <t>EORI号</t>
+  </si>
+  <si>
+    <t>收件人电话*</t>
+  </si>
+  <si>
+    <t>0790016103 或 0720335869</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>收件人电话*</t>
-  </si>
-  <si>
-    <t>0790016103/0720335869</t>
-  </si>
-  <si>
     <t>收件人邮箱</t>
   </si>
   <si>
+    <t>申报币种*</t>
+  </si>
+  <si>
+    <t>美元</t>
+  </si>
+  <si>
     <t>PO Number</t>
   </si>
   <si>
@@ -326,7 +375,7 @@
     <t>中文品名*</t>
   </si>
   <si>
-    <t>申报单价*(USD）</t>
+    <t>申报单价*</t>
   </si>
   <si>
     <t>申报数量*</t>
@@ -362,34 +411,37 @@
     <t>罗马尼亚专线空运（带电带磁）</t>
   </si>
   <si>
-    <t xml:space="preserve"> 罗马尼亚专线空运（普货）</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 美国专线-HK特快(可接带电）</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 美国专线大陆特快（不接带电）</t>
-  </si>
-  <si>
-    <t>罗马尼亚DHL小包</t>
+    <t>罗马尼亚专线空运（普货）</t>
+  </si>
+  <si>
+    <t>美国专线-HK特快(可接带电）</t>
+  </si>
+  <si>
+    <t>美国专线大陆特快(不接带电）</t>
+  </si>
+  <si>
+    <t>欧洲DHL-仿牌渠道</t>
   </si>
   <si>
     <t>欧洲新能源卡航（电池类）</t>
   </si>
   <si>
-    <t xml:space="preserve"> 欧洲海运包税</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 欧洲铁路包税</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 欧洲卡航限时达-GLS/DHL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 罗马尼亚限时达卡派</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 罗马尼亚海运</t>
+    <t>欧洲海运包税</t>
+  </si>
+  <si>
+    <t>欧洲铁路包税</t>
+  </si>
+  <si>
+    <t>欧洲卡航包税-GLS/DHL</t>
+  </si>
+  <si>
+    <t>罗马尼亚卡航</t>
+  </si>
+  <si>
+    <t>罗马尼亚铁路</t>
+  </si>
+  <si>
+    <t>罗马尼亚海运</t>
   </si>
   <si>
     <t>COSCO卡派</t>
@@ -407,22 +459,19 @@
     <t>美森加班海卡</t>
   </si>
   <si>
-    <t xml:space="preserve"> 美森加班海派</t>
+    <t>美森加班海派</t>
   </si>
   <si>
     <t>美森限时达海卡</t>
   </si>
   <si>
-    <t xml:space="preserve"> 美森限时达海派</t>
-  </si>
-  <si>
-    <t>巴西小包</t>
+    <t>美森限时达海派</t>
   </si>
   <si>
     <t>Allegro波兰铁路专线</t>
   </si>
   <si>
-    <t>Allegro波兰卡航限时达专线</t>
+    <t>Allegro波兰卡航专线</t>
   </si>
   <si>
     <t>欧洲卡航超大件卡派包税</t>
@@ -434,7 +483,7 @@
     <t>加拿大FBA海卡美森-包税</t>
   </si>
   <si>
-    <t>加拿大UPS派送美森-包税</t>
+    <t>加拿大FBA海卡普船-包税</t>
   </si>
   <si>
     <t>快递渠道</t>
@@ -473,7 +522,28 @@
     <t>英国铁路包税</t>
   </si>
   <si>
-    <t>日本空运专线</t>
+    <t>欧洲海运递延海派</t>
+  </si>
+  <si>
+    <t>以星限时达海派</t>
+  </si>
+  <si>
+    <t>欧洲海运纯电包税</t>
+  </si>
+  <si>
+    <t>欧洲海运递延卡派KG</t>
+  </si>
+  <si>
+    <t>欧洲海运递延卡派CBM</t>
+  </si>
+  <si>
+    <t>欧洲卡航自税/递延</t>
+  </si>
+  <si>
+    <t>英国空运包税</t>
+  </si>
+  <si>
+    <t>美国小包</t>
   </si>
 </sst>
 </file>
@@ -486,20 +556,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="DengXian"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <color theme="1"/>
-      <name val="DengXian"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -509,12 +578,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
@@ -548,6 +611,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
@@ -562,46 +630,47 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="DengXian"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="11"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="DengXian Light"/>
-      <charset val="0"/>
-      <scheme val="major"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="DengXian"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -609,7 +678,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="DengXian"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -617,82 +686,89 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="DengXian"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="DengXian"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -926,7 +1002,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -963,6 +1039,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -981,7 +1086,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thick">
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -990,17 +1095,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thick">
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1071,7 +1167,9 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1087,9 +1185,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1101,34 +1203,34 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1143,10 +1245,10 @@
     <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1155,10 +1257,10 @@
     <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1167,10 +1269,10 @@
     <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1179,10 +1281,10 @@
     <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1191,10 +1293,10 @@
     <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1203,99 +1305,108 @@
     <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="36">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1350,19 +1461,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors>
-    <mruColors>
-      <color rgb="00FFFF00"/>
-      <color rgb="00C00000"/>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00002060"/>
-      <color rgb="0031869B"/>
-      <color rgb="00FCD5B4"/>
-      <color rgb="00FF0000"/>
-      <color rgb="00000000"/>
-    </mruColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1372,9 +1471,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1382,44 +1481,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
-        <a:latin typeface="DengXian Light"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="DengXian Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1449,12 +1548,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="DengXian"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="DengXian"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1484,628 +1583,554 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="130000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.6"/>
   <cols>
-    <col min="1" max="1" width="21.25" style="4" customWidth="1"/>
-    <col min="2" max="5" width="13.2321428571429" style="5" customWidth="1"/>
-    <col min="6" max="6" width="11.0178571428571" style="5" customWidth="1"/>
-    <col min="7" max="10" width="13.8214285714286" style="5" customWidth="1"/>
-    <col min="11" max="15" width="11.0178571428571" style="5" customWidth="1"/>
-    <col min="16" max="16" width="13.8214285714286" style="5" customWidth="1"/>
-    <col min="17" max="17" width="11.0178571428571" style="5" customWidth="1"/>
-    <col min="18" max="16384" width="11" style="5"/>
+    <col min="1" max="1" width="21.25" style="6" customWidth="1"/>
+    <col min="2" max="5" width="13.2307692307692" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.0192307692308" style="3" customWidth="1"/>
+    <col min="7" max="10" width="13.8269230769231" style="3" customWidth="1"/>
+    <col min="11" max="15" width="11.0192307692308" style="3" customWidth="1"/>
+    <col min="16" max="16" width="13.8269230769231" style="3" customWidth="1"/>
+    <col min="17" max="17" width="11.0192307692308" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="11" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:15">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="29" t="s">
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="33"/>
+    </row>
+    <row r="2" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="31"/>
-    </row>
-    <row r="2" ht="21" customHeight="1" spans="1:15">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="F2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="33"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="21" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="31"/>
-    </row>
-    <row r="3" ht="21" customHeight="1" spans="1:15">
-      <c r="A3" s="9" t="s">
+      <c r="F3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="33"/>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="21" t="s">
+      <c r="B4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="31"/>
-    </row>
-    <row r="4" ht="21" customHeight="1" spans="1:15">
-      <c r="A4" s="6" t="s">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="F4" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="33"/>
+    </row>
+    <row r="5" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="21" t="s">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="31"/>
-    </row>
-    <row r="5" ht="21" customHeight="1" spans="1:15">
-      <c r="A5" s="12" t="s">
+      <c r="F5" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="33"/>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="32" customHeight="1" spans="1:15">
+      <c r="A6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="21" t="s">
+      <c r="B6" s="13" t="s">
         <v>14</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="31"/>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:15">
-      <c r="A6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>16</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="33"/>
+    </row>
+    <row r="7" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A7" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31"/>
-    </row>
-    <row r="7" ht="21" customHeight="1" spans="1:15">
-      <c r="A7" s="12" t="s">
-        <v>19</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="33"/>
+    </row>
+    <row r="8" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="31"/>
-    </row>
-    <row r="8" ht="21" customHeight="1" spans="1:15">
-      <c r="A8" s="6" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="F8" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="24" t="s">
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="33"/>
+    </row>
+    <row r="9" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="B9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31"/>
-    </row>
-    <row r="9" ht="21" customHeight="1" spans="1:15">
-      <c r="A9" s="12" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="33"/>
+    </row>
+    <row r="10" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="21" t="s">
+      <c r="B10" s="36" t="s">
         <v>27</v>
-      </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="31"/>
-    </row>
-    <row r="10" ht="21" customHeight="1" spans="1:15">
-      <c r="A10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>29</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="33"/>
+    </row>
+    <row r="11" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="31"/>
-    </row>
-    <row r="11" ht="21" customHeight="1" spans="1:14">
-      <c r="A11" s="6" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="21" t="s">
+      <c r="B12" s="14" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-    </row>
-    <row r="12" ht="21" customHeight="1" spans="1:14">
-      <c r="A12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>35</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-    </row>
-    <row r="13" ht="21" customHeight="1" spans="1:14">
-      <c r="A13" s="12" t="s">
-        <v>36</v>
+      <c r="E12" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+    </row>
+    <row r="13" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A13" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-    </row>
-    <row r="14" ht="21" customHeight="1" spans="1:14">
-      <c r="A14" s="12" t="s">
+      <c r="E13" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="24" t="s">
         <v>37</v>
+      </c>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+    </row>
+    <row r="14" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
+      <c r="A14" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-    </row>
-    <row r="15" ht="21" customHeight="1" spans="1:14">
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+    </row>
+    <row r="15" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A15" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="17">
-        <v>3</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B15" s="17"/>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="25"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="29" customHeight="1" spans="1:17">
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+    </row>
+    <row r="16" s="4" customFormat="1" ht="29" customHeight="1" spans="1:17">
       <c r="A16" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="28" t="s">
+      <c r="F16" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="H16" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="K16" s="28" t="s">
+      <c r="J16" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="28" t="s">
+      <c r="K16" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="28" t="s">
+      <c r="L16" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="28" t="s">
+      <c r="M16" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="28" t="s">
+      <c r="N16" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="P16" s="28" t="s">
+      <c r="O16" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="Q16" s="28" t="s">
+      <c r="P16" s="26" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="80" customHeight="1" spans="1:17">
+      <c r="Q16" s="26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
+      <c r="F17" s="27"/>
       <c r="G17" s="20"/>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
@@ -2115,15 +2140,239 @@
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
       <c r="O17" s="20"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="20"/>
-    </row>
-    <row r="18" ht="24" customHeight="1"/>
-    <row r="19" ht="24" customHeight="1"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="35"/>
+    </row>
+    <row r="18" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="35"/>
+    </row>
+    <row r="19" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="35"/>
+    </row>
+    <row r="20" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="35"/>
+    </row>
+    <row r="21" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="35"/>
+    </row>
+    <row r="22" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="35"/>
+    </row>
+    <row r="23" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="35"/>
+    </row>
+    <row r="24" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="35"/>
+    </row>
+    <row r="25" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="35"/>
+    </row>
+    <row r="26" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="35"/>
+    </row>
+    <row r="27" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="35"/>
+    </row>
+    <row r="28" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="35"/>
+    </row>
+    <row r="29" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="35"/>
+    </row>
+    <row r="30" ht="24" customHeight="1"/>
+    <row r="31" ht="24" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A16:Q17">
-    <extLst/>
-  </autoFilter>
   <mergeCells count="30">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -2156,9 +2405,9 @@
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="I1:N15"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:D2">
-      <formula1>Sheet1!$A:$A</formula1>
+      <formula1>Sheet2!$A:$A</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:H6">
       <formula1>"买单报关,报关退税"</formula1>
@@ -2169,12 +2418,15 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:H8">
       <formula1>"包税,不包税,自主税号,自税递延"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:H13">
+      <formula1>"美元,欧元,英镑"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:H5">
       <formula1>"否,是"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="257" orientation="portrait" horizontalDpi="203" verticalDpi="203"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -2183,224 +2435,256 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="29.1964285714286" customWidth="1"/>
+    <col min="1" max="1" width="29.2019230769231" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:1">
+      <c r="A1" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:1">
+      <c r="A2" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:1">
+      <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:1">
+      <c r="A4" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:1">
+      <c r="A5" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+    <row r="6" s="1" customFormat="1" spans="1:1">
+      <c r="A6" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:1">
+      <c r="A7" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:1">
+      <c r="A8" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="9" s="1" customFormat="1" spans="1:1">
+      <c r="A9" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+    <row r="10" s="1" customFormat="1" spans="1:1">
+      <c r="A10" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+    <row r="11" s="1" customFormat="1" spans="1:1">
+      <c r="A11" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
+    <row r="12" s="1" customFormat="1" spans="1:1">
+      <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
+    <row r="13" s="1" customFormat="1" spans="1:1">
+      <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+    <row r="14" s="1" customFormat="1" spans="1:1">
+      <c r="A14" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
+    <row r="15" s="1" customFormat="1" spans="1:1">
+      <c r="A15" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
+    <row r="16" s="1" customFormat="1" spans="1:1">
+      <c r="A16" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
+    <row r="17" s="1" customFormat="1" spans="1:1">
+      <c r="A17" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
+    <row r="18" s="1" customFormat="1" spans="1:1">
+      <c r="A18" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:1">
+      <c r="A19" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+    <row r="20" s="1" customFormat="1" spans="1:1">
+      <c r="A20" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+    <row r="21" s="1" customFormat="1" spans="1:1">
+      <c r="A21" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
+    <row r="22" s="1" customFormat="1" spans="1:1">
+      <c r="A22" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
+    <row r="23" s="1" customFormat="1" spans="1:1">
+      <c r="A23" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
+    <row r="24" s="1" customFormat="1" spans="1:1">
+      <c r="A24" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
+    <row r="25" s="1" customFormat="1" spans="1:1">
+      <c r="A25" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
+    <row r="26" s="1" customFormat="1" spans="1:1">
+      <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
+    <row r="27" s="1" customFormat="1" spans="1:1">
+      <c r="A27" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
+    <row r="28" s="1" customFormat="1" spans="1:1">
+      <c r="A28" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
+    <row r="29" s="1" customFormat="1" spans="1:1">
+      <c r="A29" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" ht="17.6" spans="1:1">
-      <c r="A32" s="1" t="s">
+    <row r="30" s="1" customFormat="1" spans="1:1">
+      <c r="A30" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
+    <row r="31" s="1" customFormat="1" spans="1:1">
+      <c r="A31" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
+    <row r="32" s="1" customFormat="1" spans="1:1">
+      <c r="A32" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
+    <row r="33" s="1" customFormat="1" spans="1:1">
+      <c r="A33" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
+    <row r="34" s="1" customFormat="1" spans="1:1">
+      <c r="A34" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
+    <row r="35" s="1" customFormat="1" spans="1:1">
+      <c r="A35" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
+    <row r="36" s="1" customFormat="1" spans="1:1">
+      <c r="A36" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
+    <row r="37" s="1" customFormat="1" spans="1:1">
+      <c r="A37" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
+    <row r="38" s="1" customFormat="1" spans="1:1">
+      <c r="A38" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+    <row r="39" s="1" customFormat="1" spans="1:1">
+      <c r="A39" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
+    <row r="40" s="1" customFormat="1" spans="1:1">
+      <c r="A40" s="2" t="s">
         <v>96</v>
       </c>
     </row>
+    <row r="41" s="1" customFormat="1" spans="1:1">
+      <c r="A41" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:1">
+      <c r="A42" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/表格模版/依诺达.xlsx
+++ b/表格模版/依诺达.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24460" windowHeight="9600"/>
+    <workbookView windowWidth="28980" windowHeight="13920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -556,7 +556,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -607,11 +607,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1002,7 +997,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1042,26 +1037,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1185,137 +1160,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1382,19 +1357,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1720,7 +1686,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.6"/>
   <cols>
     <col min="1" max="1" width="21.25" style="6" customWidth="1"/>
@@ -1748,15 +1714,15 @@
       </c>
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="33"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="30"/>
     </row>
     <row r="2" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A2" s="7" t="s">
@@ -1773,13 +1739,13 @@
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="33"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="30"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A3" s="10" t="s">
@@ -1796,13 +1762,13 @@
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="33"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="30"/>
     </row>
     <row r="4" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A4" s="7" t="s">
@@ -1821,13 +1787,13 @@
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="33"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="30"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A5" s="10" t="s">
@@ -1844,13 +1810,13 @@
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="33"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="30"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="32" customHeight="1" spans="1:15">
       <c r="A6" s="7" t="s">
@@ -1869,13 +1835,13 @@
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="33"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="30"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A7" s="10" t="s">
@@ -1890,13 +1856,13 @@
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="33"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="30"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A8" s="7" t="s">
@@ -1915,13 +1881,13 @@
       </c>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="33"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="30"/>
     </row>
     <row r="9" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A9" s="10" t="s">
@@ -1938,19 +1904,19 @@
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="33"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="30"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="21" customHeight="1" spans="1:15">
       <c r="A10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="33" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="14"/>
@@ -1961,13 +1927,13 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="33"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="30"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A11" s="7" t="s">
@@ -1984,12 +1950,12 @@
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A12" s="7" t="s">
@@ -2006,12 +1972,12 @@
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A13" s="10" t="s">
@@ -2028,12 +1994,12 @@
       </c>
       <c r="G13" s="24"/>
       <c r="H13" s="24"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A14" s="10" t="s">
@@ -2046,12 +2012,12 @@
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="21" customHeight="1" spans="1:14">
       <c r="A15" s="16" t="s">
@@ -2064,12 +2030,12 @@
       <c r="F15" s="17"/>
       <c r="G15" s="17"/>
       <c r="H15" s="17"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
     </row>
     <row r="16" s="4" customFormat="1" ht="29" customHeight="1" spans="1:17">
       <c r="A16" s="18" t="s">
@@ -2124,7 +2090,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
+    <row r="17" s="5" customFormat="1" ht="95" customHeight="1" spans="1:17">
       <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -2140,238 +2106,11 @@
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
       <c r="O17" s="20"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="35"/>
-    </row>
-    <row r="18" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="35"/>
-    </row>
-    <row r="19" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="35"/>
-    </row>
-    <row r="20" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="35"/>
-    </row>
-    <row r="21" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="35"/>
-    </row>
-    <row r="22" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="35"/>
-    </row>
-    <row r="23" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="35"/>
-    </row>
-    <row r="24" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="34"/>
-      <c r="Q24" s="35"/>
-    </row>
-    <row r="25" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="34"/>
-      <c r="Q25" s="35"/>
-    </row>
-    <row r="26" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="35"/>
-    </row>
-    <row r="27" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="35"/>
-    </row>
-    <row r="28" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="35"/>
-    </row>
-    <row r="29" s="5" customFormat="1" ht="24" customHeight="1" spans="1:17">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="35"/>
-    </row>
-    <row r="30" ht="24" customHeight="1"/>
-    <row r="31" ht="24" customHeight="1"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="32"/>
+    </row>
+    <row r="18" ht="24" customHeight="1"/>
+    <row r="19" ht="24" customHeight="1"/>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="B1:D1"/>

--- a/表格模版/依诺达.xlsx
+++ b/表格模版/依诺达.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28980" windowHeight="13920"/>
+    <workbookView windowWidth="16980" windowHeight="9860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
   <si>
     <t>客户订单号*</t>
   </si>
@@ -254,7 +254,7 @@
     <t>收件人地址一*</t>
   </si>
   <si>
-    <t>StradaCiorogarla214,RampaS35-S36</t>
+    <t>Strada Ciorogarla 214, sat Bacu, Comuna Joita, judet Giurgiu, Rampa N37-38</t>
   </si>
   <si>
     <r>
@@ -291,7 +291,7 @@
     <t>收件人城市*</t>
   </si>
   <si>
-    <t>Bâcu</t>
+    <t>comuna Joita, sat Bacu</t>
   </si>
   <si>
     <t>交税方式*</t>
@@ -330,7 +330,7 @@
     <t>收件人电话*</t>
   </si>
   <si>
-    <t>0790016103 或 0720335869</t>
+    <t>0790016103/0720335869</t>
   </si>
   <si>
     <t>备注</t>
@@ -402,148 +402,148 @@
     <t>图片*</t>
   </si>
   <si>
-    <t>欧洲空运双清包税-大陆飞</t>
-  </si>
-  <si>
-    <t>欧洲空运双清包税-带电</t>
-  </si>
-  <si>
-    <t>罗马尼亚专线空运（带电带磁）</t>
-  </si>
-  <si>
-    <t>罗马尼亚专线空运（普货）</t>
-  </si>
-  <si>
-    <t>美国专线-HK特快(可接带电）</t>
-  </si>
-  <si>
-    <t>美国专线大陆特快(不接带电）</t>
-  </si>
-  <si>
-    <t>欧洲DHL-仿牌渠道</t>
-  </si>
-  <si>
-    <t>欧洲新能源卡航（电池类）</t>
-  </si>
-  <si>
-    <t>欧洲海运包税</t>
-  </si>
-  <si>
-    <t>欧洲铁路包税</t>
-  </si>
-  <si>
-    <t>欧洲卡航包税-GLS/DHL</t>
-  </si>
-  <si>
-    <t>罗马尼亚卡航</t>
-  </si>
-  <si>
-    <t>罗马尼亚铁路</t>
-  </si>
-  <si>
-    <t>罗马尼亚海运</t>
-  </si>
-  <si>
-    <t>COSCO卡派</t>
-  </si>
-  <si>
-    <t>COSCO快线海派</t>
-  </si>
-  <si>
-    <t>盐田定提海派</t>
-  </si>
-  <si>
-    <t>美国海卡包税</t>
-  </si>
-  <si>
-    <t>美森加班海卡</t>
-  </si>
-  <si>
-    <t>美森加班海派</t>
-  </si>
-  <si>
-    <t>美森限时达海卡</t>
-  </si>
-  <si>
-    <t>美森限时达海派</t>
-  </si>
-  <si>
-    <t>Allegro波兰铁路专线</t>
-  </si>
-  <si>
-    <t>Allegro波兰卡航专线</t>
-  </si>
-  <si>
-    <t>欧洲卡航超大件卡派包税</t>
-  </si>
-  <si>
-    <t>欧洲海运递延整柜</t>
-  </si>
-  <si>
-    <t>加拿大FBA海卡美森-包税</t>
-  </si>
-  <si>
-    <t>加拿大FBA海卡普船-包税</t>
-  </si>
-  <si>
-    <t>快递渠道</t>
-  </si>
-  <si>
-    <t>欧洲特敏小包DPD</t>
-  </si>
-  <si>
-    <t>法国cdiscount海运专线</t>
-  </si>
-  <si>
-    <t>法国cdiscount卡航专线</t>
-  </si>
-  <si>
-    <t>法国cdiscount铁路专线</t>
-  </si>
-  <si>
-    <t>法国cdiscount递延</t>
-  </si>
-  <si>
-    <t>英国卡航自税</t>
-  </si>
-  <si>
-    <t>英国卡航包税</t>
-  </si>
-  <si>
-    <t>英国海运自税</t>
-  </si>
-  <si>
-    <t>英国海运包税</t>
-  </si>
-  <si>
-    <t>英国铁路自税</t>
-  </si>
-  <si>
-    <t>英国铁路包税</t>
-  </si>
-  <si>
-    <t>欧洲海运递延海派</t>
-  </si>
-  <si>
-    <t>以星限时达海派</t>
-  </si>
-  <si>
-    <t>欧洲海运纯电包税</t>
-  </si>
-  <si>
-    <t>欧洲海运递延卡派KG</t>
-  </si>
-  <si>
-    <t>欧洲海运递延卡派CBM</t>
-  </si>
-  <si>
-    <t>欧洲卡航自税/递延</t>
-  </si>
-  <si>
-    <t>英国空运包税</t>
-  </si>
-  <si>
-    <t>美国小包</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>欧洲空运双清包税-大陆飞</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>欧洲空运双清包税-带电</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>罗马尼亚专线空运（带电带磁）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>罗马尼亚专线空运（普货）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>欧洲海运包税</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>欧洲铁路包税</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>欧洲卡航包税-GLS/DHL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>罗马尼亚卡航</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>罗马尼亚铁路</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>罗马尼亚海运</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Allegro波兰铁路专线</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Allegro波兰卡航专线</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1799,7 +1799,9 @@
       <c r="A5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="21" t="s">
@@ -2174,252 +2176,150 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="29.2019230769231" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:1">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:1">
-      <c r="A2" s="2" t="s">
+    <row r="2" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:1">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:1">
-      <c r="A4" s="2" t="s">
+    <row r="4" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:1">
-      <c r="A5" s="2" t="s">
+    <row r="5" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:1">
-      <c r="A6" s="2" t="s">
+    <row r="6" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:1">
-      <c r="A7" s="2" t="s">
+    <row r="7" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:1">
-      <c r="A8" s="2" t="s">
+    <row r="8" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:1">
-      <c r="A9" s="2" t="s">
+    <row r="9" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:1">
-      <c r="A10" s="2" t="s">
+    <row r="10" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:1">
-      <c r="A11" s="2" t="s">
+    <row r="11" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:1">
-      <c r="A12" s="2" t="s">
+    <row r="12" s="1" customFormat="1" ht="17" spans="1:1">
+      <c r="A12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:1">
-      <c r="A13" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
+    <row r="13" s="1" customFormat="1"/>
     <row r="14" s="1" customFormat="1" spans="1:1">
-      <c r="A14" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:1">
-      <c r="A15" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
+      <c r="A14"/>
+    </row>
+    <row r="15" s="1" customFormat="1"/>
     <row r="16" s="1" customFormat="1" spans="1:1">
-      <c r="A16" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:1">
-      <c r="A17" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
+      <c r="A16"/>
+    </row>
+    <row r="17" s="1" customFormat="1"/>
     <row r="18" s="1" customFormat="1" spans="1:1">
-      <c r="A18" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:1">
-      <c r="A19" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
+      <c r="A18"/>
+    </row>
+    <row r="19" s="1" customFormat="1"/>
     <row r="20" s="1" customFormat="1" spans="1:1">
-      <c r="A20" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:1">
-      <c r="A21" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
+      <c r="A20"/>
+    </row>
+    <row r="21" s="1" customFormat="1"/>
     <row r="22" s="1" customFormat="1" spans="1:1">
-      <c r="A22" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:1">
-      <c r="A23" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
+      <c r="A22"/>
+    </row>
+    <row r="23" s="1" customFormat="1"/>
     <row r="24" s="1" customFormat="1" spans="1:1">
-      <c r="A24" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="A24" s="2"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:1">
-      <c r="A25" s="2" t="s">
-        <v>81</v>
-      </c>
+      <c r="A25" s="2"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:1">
-      <c r="A26" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="A26" s="2"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:1">
-      <c r="A27" s="2" t="s">
-        <v>83</v>
-      </c>
+      <c r="A27" s="2"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:1">
-      <c r="A28" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="A28" s="2"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:1">
-      <c r="A29" s="2" t="s">
-        <v>85</v>
-      </c>
+      <c r="A29" s="2"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:1">
-      <c r="A30" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="A30" s="2"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:1">
-      <c r="A31" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="A31" s="2"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:1">
-      <c r="A32" s="2" t="s">
-        <v>88</v>
-      </c>
+      <c r="A32" s="2"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:1">
-      <c r="A33" s="2" t="s">
-        <v>89</v>
-      </c>
+      <c r="A33" s="2"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:1">
-      <c r="A34" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="A34" s="2"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:1">
-      <c r="A35" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="A35" s="2"/>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:1">
-      <c r="A36" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A36" s="2"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:1">
-      <c r="A37" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="A37" s="2"/>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:1">
-      <c r="A38" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A38" s="2"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:1">
-      <c r="A39" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="A39" s="2"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:1">
-      <c r="A40" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="A40" s="2"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:1">
-      <c r="A41" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="A41" s="2"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:1">
-      <c r="A42" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="2" t="s">
-        <v>104</v>
-      </c>
+      <c r="A42" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
